--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Staff/AdminApp_Staff_tab_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Staff/AdminApp_Staff_tab_test_cases.xlsx
@@ -2868,7 +2868,7 @@
         <v>24</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>24</v>
@@ -2912,7 +2912,7 @@
         <v>24</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="N29" s="2" t="s">
         <v>24</v>
@@ -3088,7 +3088,7 @@
         <v>24</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="N33" s="2" t="s">
         <v>24</v>
@@ -3176,7 +3176,7 @@
         <v>24</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="N35" s="2" t="s">
         <v>24</v>
@@ -3264,7 +3264,7 @@
         <v>24</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="N37" s="2" t="s">
         <v>24</v>
@@ -3308,7 +3308,7 @@
         <v>24</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="N38" s="2" t="s">
         <v>24</v>
@@ -3440,7 +3440,7 @@
         <v>24</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="N41" s="2" t="s">
         <v>24</v>
@@ -3484,7 +3484,7 @@
         <v>24</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="N42" s="2" t="s">
         <v>24</v>
@@ -3572,7 +3572,7 @@
         <v>24</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="N44" s="2" t="s">
         <v>24</v>

--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Staff/AdminApp_Staff_tab_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Staff/AdminApp_Staff_tab_test_cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="386">
   <si>
     <t>S.No.</t>
   </si>
@@ -1234,6 +1234,12 @@
   </si>
   <si>
     <t>Added 2026-09-01 from the other team's TC_STF_009, whose step 3 is "log in as that user and confirm admin console access". Our TST_STFP_TC_10 stops at the role label changing in the UI - which a grant that updated the display but not the permission would also satisfy. This is the same shape as the Students password gap (TST_SPRF_TC_23): we verify the UI acknowledged the change, not that the change took effect. Mutates a real account - data-mutating suite, and revoke the rights afterwards as housekeeping.</t>
+  </si>
+  <si>
+    <t>Promoted teacher successfully accessed Admin Console (Classes and Staff tabs) on Thor, and admin rights were cleanly revoked in teardown.</t>
+  </si>
+  <si>
+    <t>Suite: adminStaffProfile (Suite2) | 2026-09-18: Pass</t>
   </si>
   <si>
     <t>TST_STFP_TC_20</t>
@@ -4508,19 +4514,19 @@
         <v>374</v>
       </c>
       <c r="L57" s="3" t="s">
-        <v>26</v>
+        <v>375</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O57" s="3" t="s">
-        <v>182</v>
+        <v>38</v>
       </c>
       <c r="P57" s="3" t="s">
-        <v>183</v>
+        <v>376</v>
       </c>
     </row>
     <row r="58" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4528,13 +4534,13 @@
         <v>57</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>94</v>
@@ -4543,19 +4549,19 @@
         <v>20</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>26</v>
@@ -4564,7 +4570,7 @@
         <v>359</v>
       </c>
       <c r="N58" s="3" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>359</v>

--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Staff/AdminApp_Staff_tab_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Staff/AdminApp_Staff_tab_test_cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="281">
   <si>
     <t>S.No.</t>
   </si>
@@ -61,13 +61,13 @@
     <t>Automation Evidence</t>
   </si>
   <si>
-    <t>TST_STFL_TC_1</t>
-  </si>
-  <si>
-    <t>Verify the Staff tab loads with all expected components when the school is opened by an administrator</t>
-  </si>
-  <si>
-    <t>— Staff tab load (added, not in source)</t>
+    <t>TST_STFL_TC_2</t>
+  </si>
+  <si>
+    <t>Verify matching staff are returned when a full first name is searched</t>
+  </si>
+  <si>
+    <t>#1 — Verify search by first name</t>
   </si>
   <si>
     <t>Positive</t>
@@ -77,41 +77,6 @@
   </si>
   <si>
     <t>Logged in as school admin testt1@mailsac.com on thor. School FCN-CHZ-PDA ("3 July Test School 1") opened from "My school accounts" BY KEY. Staff tab open at /admin/admin/org_perf_testschool_1/staff.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open school "3 July Test School 1" by key FCN-CHZ-PDA from "My school accounts".
-2. Click "Staff" in the left navigation.
-3. Observe the page.</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>The URL is /admin/admin/org_&lt;slug&gt;/staff and the browser tab reads "Staff | Cambridge One". The page shows: heading Staff (N); a search box placeholder Search by first name, last name or email with a Search button; a Manage staff menu; a collapsed User guide toggle; a sortable table headed Last name | First name | Email address | Role, sorted by Last name ascending; up to 20 staff rows; and Load more ... when more than 20 staff exist.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Column set differs from the Students tab — there is a Role column and there is NO row-selection checkbox, no N Selected counter and no bulk "Remove from school account" on the list. Role values seen: Teacher, Administrator/Teacher.</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Not Run</t>
-  </si>
-  <si>
-    <t>Excluded - Phase 1</t>
-  </si>
-  <si>
-    <t>Out of Phase 1 automation scope.</t>
-  </si>
-  <si>
-    <t>TST_STFL_TC_2</t>
-  </si>
-  <si>
-    <t>Verify matching staff are returned when a full first name is searched</t>
-  </si>
-  <si>
-    <t>#1 — Verify search by first name</t>
   </si>
   <si>
     <t xml:space="preserve">1. Type teacher19oct in the search box.
@@ -128,13 +93,16 @@
     <t>Search covers first name, last name and email from the single box.</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>Pass</t>
   </si>
   <si>
     <t>Automated</t>
   </si>
   <si>
-    <t>Suite: adminStaffTab | 2026-09-16: Pass across 2 runs</t>
+    <t>Suite: adminStaffTab | Not executed in this audit - status carried over, treat as unverified</t>
   </si>
   <si>
     <t>TST_STFL_TC_3</t>
@@ -183,26 +151,6 @@
     <t>Case-preserving echo is confirmed behaviour on the sibling Students tab and re-observed here.</t>
   </si>
   <si>
-    <t>TST_STFL_TC_5</t>
-  </si>
-  <si>
-    <t>Verify the list is unchanged when a search term is typed but the Search button is not clicked</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Type gg in the search box.
-2. Do NOT click Search. Wait 3 s.
-3. Observe the heading and rows.</t>
-  </si>
-  <si>
-    <t>gg</t>
-  </si>
-  <si>
-    <t>The list is not filtered — the heading still reads Staff (N) and the same rows are shown. Search is submit-driven, not live.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-24: typing alone left the heading at Staff (23).</t>
-  </si>
-  <si>
     <t>TST_STFL_TC_6</t>
   </si>
   <si>
@@ -225,25 +173,6 @@
     <t>Verified live 2026-08-24 — exactly these two rows returned.</t>
   </si>
   <si>
-    <t>TST_STFL_TC_7</t>
-  </si>
-  <si>
-    <t>Verify the full staff list is restored when Clear is clicked after a search</t>
-  </si>
-  <si>
-    <t>Logged in as school admin testt1@mailsac.com on thor. School FCN-CHZ-PDA ("3 July Test School 1") opened from "My school accounts" BY KEY. Staff tab open at /admin/admin/org_perf_testschool_1/staff. A search for gg has been submitted.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click Clear in the search banner.
-2. Observe the heading, the search box and the rows.</t>
-  </si>
-  <si>
-    <t>The banner is replaced by the Staff (N) count heading, the search box is emptied, the first page of 20 staff is shown again and Load more ... reappears.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-24: heading returned to Staff (23), box empty, 20 rows, Load more present.</t>
-  </si>
-  <si>
     <t>TST_STFL_TC_8</t>
   </si>
   <si>
@@ -263,6 +192,9 @@
     <t>Exactly one row is listed — gg | testteacher18 | testteacher18oct@mailsac.com | Administrator/Teacher — and the banner echoes the full address.</t>
   </si>
   <si>
+    <t>—</t>
+  </si>
+  <si>
     <t>TST_STFL_TC_9</t>
   </si>
   <si>
@@ -280,28 +212,6 @@
   </si>
   <si>
     <t>Nine Perf Test rows carried @yopmail.com at capture; do not assert the number.</t>
-  </si>
-  <si>
-    <t>TST_STFL_TC_10</t>
-  </si>
-  <si>
-    <t>Verify the search banner state is entered and every staff member returned when the term is whitespace only</t>
-  </si>
-  <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Type three spaces in the search box.
-2. Click Search.</t>
-  </si>
-  <si>
-    <t>Three space characters</t>
-  </si>
-  <si>
-    <t>The term is trimmed to nothing, but the page still enters the search banner state — the count heading is replaced by Showing search results for . with Clear — and every staff member is returned. [ASSUMED] — not exercised live on the Staff tab; this is the confirmed Students-tab behaviour.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. [ASSUMED]. Entering the banner state on an empty term is arguably wrong; it is recorded as an observation, not a defect case. Confirm during Phase 1.</t>
   </si>
   <si>
     <t>TST_STFL_TC_11</t>
@@ -481,25 +391,6 @@
   </si>
   <si>
     <t>Verified live 2026-08-24. Same collation rule as the Classes and Students tabs (admin-shared.md §A4).</t>
-  </si>
-  <si>
-    <t>TST_STFL_TC_21</t>
-  </si>
-  <si>
-    <t>Verify the list returns to the first page of 20 when the sort column is changed after Load more</t>
-  </si>
-  <si>
-    <t>Logged in as school admin testt1@mailsac.com on thor. School FCN-CHZ-PDA ("3 July Test School 1") opened from "My school accounts" BY KEY. Staff tab open at /admin/admin/org_perf_testschool_1/staff. Load more ... has been clicked so the full list is rendered and the link has gone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click any column header to change the sort.
-2. Count the rendered rows and look for Load more ....</t>
-  </si>
-  <si>
-    <t>The list is truncated back to the first 20 rows in the new order and Load more ... is present again.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-24 — sorting resets pagination.</t>
   </si>
   <si>
     <t>TST_STFL_TC_23</t>
@@ -553,25 +444,10 @@
 4. Look for Load more ... again.</t>
   </si>
   <si>
+    <t>gg</t>
+  </si>
+  <si>
     <t>Load more ... is absent while the two-row result set is shown, and reappears after Clear restores the full list.</t>
-  </si>
-  <si>
-    <t>TST_STFL_TC_26</t>
-  </si>
-  <si>
-    <t>Verify the heading count matches the number of staff rows when the whole list has been loaded</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Read the count in the heading Staff (N).
-2. Click Load more ... until it is removed from the page.
-3. Count the rendered staff rows.
-4. Compare the two numbers.</t>
-  </si>
-  <si>
-    <t>Expected: the number of rendered rows equals the heading count. Actual (verified live 2026-08-24): the heading read Staff (23) but the exhausted list rendered only 21 unique rows — a shortfall of 2 with Load more ... already removed.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Expected-versus-actual — a real defect, confirmed with the team 2026-08-24. The count is NOT explained by pending invitations: the team confirmed that Staff (N) increments only when an invited teacher ACCEPTS, so invited-but-not-joined staff are not counted. The 2-row shortfall is therefore unexplained. It may be specific to this school's data. Because the school is shared, automate this as "heading count equals rendered row count", never as the literal numbers 23 and 21 — and expect this case to FAIL on FCN-CHZ-PDA until the data or the defect is fixed.</t>
   </si>
   <si>
     <t>TST_STFL_TC_27</t>
@@ -602,6 +478,9 @@
     <t>Sends real email and creates a real account — mailsac/yopmail addresses only, prefix AutoStaff_. The count timing is now confirmed (acceptance, not invitation), so this case is no longer [ASSUMED] on that point; what remains unverified is the end-to-end run itself. Note TST_STFL_TC_26: the heading count and the rendered rows already disagree by 2 on this school, so assert the DELTA on the count, not the row total.</t>
   </si>
   <si>
+    <t>Not Run</t>
+  </si>
+  <si>
     <t>Not Automated</t>
   </si>
   <si>
@@ -631,7 +510,7 @@
     <t>The row itself is the menu toggle — the whole row is a button with data-toggle="dropdown", and the menu holds exactly ONE item, View profile. There is no "Activate course materials" item as there is on the Students tab. teacher17aug2026@mailsac.com is the team-nominated teacher fixture for this school [confirmed with the team 2026-08-24].</t>
   </si>
   <si>
-    <t>Suite: adminStaffProfile | 2026-09-16: Pass across 2 runs</t>
+    <t>Suite: adminStaffProfile | Not executed in this audit - status carried over, treat as unverified</t>
   </si>
   <si>
     <t>TST_STFP_TC_2</t>
@@ -648,69 +527,6 @@
   </si>
   <si>
     <t>The profile shows the heading gg, testteacher18 and the role line reads Administrator/Teacher, matching the Role column on the list.</t>
-  </si>
-  <si>
-    <t>TST_STFP_TC_3</t>
-  </si>
-  <si>
-    <t>Verify the Staff tab is restored when Back is clicked on a staff profile</t>
-  </si>
-  <si>
-    <t>Logged in as school admin testt1@mailsac.com on thor. School FCN-CHZ-PDA ("3 July Test School 1") opened from "My school accounts" BY KEY. Staff tab open at /admin/admin/org_perf_testschool_1/staff. A staff profile has been opened via the row action menu &gt; "View profile" (the profile URL is NOT deep-linkable, so a staff profile cannot be reached directly).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click Back.
-2. Observe the page.</t>
-  </si>
-  <si>
-    <t>The Staff tab is shown again at /admin/admin/org_&lt;slug&gt;/staff, in its default state — heading Staff (N), sorted by Last name ascending, first page of 20 rows.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-24. Any search or sort applied before opening the profile is NOT preserved on return — check this explicitly during Phase 1 if a test depends on it.</t>
-  </si>
-  <si>
-    <t>TST_STFP_TC_4</t>
-  </si>
-  <si>
-    <t>Verify an empty-state message is shown when the staff member belongs to no classes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open the profile of teacher17aug2026@mailsac.com, who teaches no classes.
-2. Read the classes section.</t>
-  </si>
-  <si>
-    <t>Teacher with no classes: teacher17aug2026@mailsac.com</t>
-  </si>
-  <si>
-    <t>The classes section shows No class with Your classes will appear here and an Add classes control, instead of a Classes (N) list.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-24 on two separate profiles. [ASSUMED] that teacher17aug2026@mailsac.com also has no classes — confirm on the first run and swap the fixture if it does.</t>
-  </si>
-  <si>
-    <t>TST_STFP_TC_6</t>
-  </si>
-  <si>
-    <t>Verify a user-visible error is shown and the page stays usable when the profile request fails</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Locate the row Perf Test | tch_L_20240705-095330_1_FCN-CHZ-PDA | ...@yopmail.com | Teacher.
-2. Open its action menu and click View profile.
-3. Observe the page for any error message.
-4. Without reloading, try to click a different staff row.
-5. Check the network panel for the getUserDetailWithClasses response.</t>
-  </si>
-  <si>
-    <t>Known-bad data fixture: tch_L_20240705-095330_1_FCN-CHZ-PDA@yopmail.com</t>
-  </si>
-  <si>
-    <t>Expected: the user sees an error explaining that the profile could not be loaded, and the Staff list remains usable — a different row can still be opened. Actual (verified live 2026-08-24): nothing is shown at all, the app silently stays on the list, and the #loader-container overlay is left visible so every subsequent row click is intercepted until the page is reloaded.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Expected-versus-actual, scoped to CLIENT-SIDE ERROR HANDLING only. The underlying HTTP 500 from getUserDetailWithClasses is a KNOWN DATA ISSUE on this one account — confirmed with the team 2026-08-24 — and is NOT part of this case; do not raise it as a product defect. What remains product-side is that any 500 produces no message and a stuck overlay. The 500 account is retained deliberately as the trigger fixture; teacher17aug2026@mailsac.com is the healthy teacher fixture used elsewhere.</t>
-  </si>
-  <si>
-    <t>HTTP 500 confirmed as a known data issue with the team, 2026-08-24. Case narrowed to the missing error handling and the stuck loading overlay.</t>
   </si>
   <si>
     <t>TST_STFP_TC_7</t>
@@ -734,25 +550,6 @@
   </si>
   <si>
     <t>Verified live 2026-08-24. Each listed class is a real link (user-profile-6-&lt;index&gt;). Contrast with the student profile, where the umbrella name is plain text with no link — do not assume the two profiles behave alike. Crossing from admin to class is a full page load, not an Angular route change; budget for it.</t>
-  </si>
-  <si>
-    <t>TST_STFP_TC_8</t>
-  </si>
-  <si>
-    <t>Verify each listed class shows its dates, join date and class key on a staff profile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open the profile of testt1@mailsac.com.
-2. Read the Classes (3) section.</t>
-  </si>
-  <si>
-    <t>Staff with classes: testt1@mailsac.com</t>
-  </si>
-  <si>
-    <t>The heading reads Classes (N) and each entry shows the class name, its date range, Date joined: &lt;date&gt;, Class key: &lt;key&gt; and the course material name — e.g. A11y test / Jul 11, 2025 - Jul 10, 2026 / Date joined: Jul 11, 2025 / Class key: iCmL-9Y8J / Collaborate 3 (NLP).</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-24. Launching an ended class shows the class page with the banner As this class ended over a month ago, you can no longer reactivate it. and a Class ended status.</t>
   </si>
   <si>
     <t>TST_STFP_TC_9</t>
@@ -865,29 +662,6 @@
     <t>[ASSUMED]. Mutating — run only against an account this suite created.</t>
   </si>
   <si>
-    <t>TST_STFP_TC_14</t>
-  </si>
-  <si>
-    <t>Verify the administrator can reach Remove admin rights on their own staff profile</t>
-  </si>
-  <si>
-    <t>Logged in as school admin testt1@mailsac.com on thor. School FCN-CHZ-PDA ("3 July Test School 1") opened from "My school accounts" BY KEY. Staff tab open at /admin/admin/org_perf_testschool_1/staff. The profile of the signed-in administrator testt1@mailsac.com is open.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click Manage account.
-2. Read the menu items.
-3. Do NOT confirm.</t>
-  </si>
-  <si>
-    <t>Own account: testt1@mailsac.com</t>
-  </si>
-  <si>
-    <t>Remove admin rights and Remove from school account are both offered on the administrator's own profile — the product does not exclude the signed-in user from either action.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-24 (menu inspected only). Never confirm either action on this account — it is the login used by every admin suite, and self-revoking would lock the whole programme out. Worth raising: should self-revocation and self-removal be prevented, or at least warned about?</t>
-  </si>
-  <si>
     <t>TST_STFP_TC_15</t>
   </si>
   <si>
@@ -895,6 +669,9 @@
   </si>
   <si>
     <t>#10 — Verify remove from school account</t>
+  </si>
+  <si>
+    <t>Logged in as school admin testt1@mailsac.com on thor. School FCN-CHZ-PDA ("3 July Test School 1") opened from "My school accounts" BY KEY. Staff tab open at /admin/admin/org_perf_testschool_1/staff. A staff profile has been opened via the row action menu &gt; "View profile" (the profile URL is NOT deep-linkable, so a staff profile cannot be reached directly).</t>
   </si>
   <si>
     <t xml:space="preserve">1. Click Manage account &gt; Remove from school account.
@@ -1069,63 +846,6 @@
     <t>Dialog copy captured verbatim from the pre-rendered DOM, 2026-08-24; the send itself was not performed. Sends real email — mailsac/yopmail addresses only, prefix AutoStaff_. Two copy defects visible in this dialog: school Account (stray capital A) and the missing space after each class.</t>
   </si>
   <si>
-    <t>TST_STFB_TC_5</t>
-  </si>
-  <si>
-    <t>Verify the bulk row actions are unavailable when no rows are selected</t>
-  </si>
-  <si>
-    <t>The invitation form is open with no row checkboxes ticked.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Confirm the counter reads 0 Selected.
-2. Observe Add role, + Add class key and Remove.</t>
-  </si>
-  <si>
-    <t>All three bulk actions are presented as unavailable while 0 Selected is shown.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-24. Automation trap: these three controls carry no qid and are disabled by the CSS class disable (not disabled, and with no native disabled property). Resolve them by their text and assert on the class.</t>
-  </si>
-  <si>
-    <t>TST_STFB_TC_6</t>
-  </si>
-  <si>
-    <t>Verify a previously saved draft is restored when the invitation form is re-opened</t>
-  </si>
-  <si>
-    <t>A draft invitation has previously been entered on this form and left unsent.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open Manage staff &gt; Add new teachers to classes.
-2. Observe the grid rows and the area above it.</t>
-  </si>
-  <si>
-    <t>The form is not empty — the previously entered rows are restored, a Saved &lt;age&gt; indicator is shown (e.g. Saved 30+ days ago), the submit button counts the restored rows, and any validation messages on those rows are already displayed.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-24 — the form opened showing Saved 30+ days ago, four restored rows and live validation messages. Same auto-save/restore behaviour as the Create new classes form (admin-shared.md §A4). A test that assumes an empty form will fail, and the draft is shared state on a shared school — do not assume your own suite wrote it.</t>
-  </si>
-  <si>
-    <t>TST_STFB_TC_7</t>
-  </si>
-  <si>
-    <t>Verify the submit button is unavailable while any invitation row is incomplete</t>
-  </si>
-  <si>
-    <t>The invitation form is open with at least one row missing a required value.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Leave a row without a role or without a valid class key.
-2. Observe the Send N invites button.</t>
-  </si>
-  <si>
-    <t>The Send N invites button is unavailable while any row fails validation.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-24 — the button was both natively disabled and carried the disabled class in this state.</t>
-  </si>
-  <si>
     <t>TST_STFB_TC_9</t>
   </si>
   <si>
@@ -1150,117 +870,61 @@
     <t>Fixture written 2026-08-24 from the real downloaded template, headers verified. It omits the template example row and uses class key wLE3-zTx6 (AutoClass_CreateOnly, active Aug 24 2026 - Sep 15 2026) — an auto-created class this programme already owns. If that class has been swept, substitute any active class key from the Classes tab. [ASSUMED] whether the Role value must be exactly Teacher (the template example uses Student) and whether the example row must be removed before upload — resolve both on the first run. During upload the product shows Please wait, this may takea few minutes — note the missing space in takea, a copy defect to raise. On failure it shows Sorry, your file could not be uploaded with the ptsupport@cambridge.org contact.</t>
   </si>
   <si>
-    <t>TST_STFB_TC_8</t>
-  </si>
-  <si>
-    <t>Verify per-field validation messages are shown when invitation rows are incomplete or invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Leave the Role cell of a populated row empty.
-2. Enter an invalid class key in another row.
-3. Leave the Email cell of a row that has a role empty.
-4. Read the messages under each cell.</t>
-  </si>
-  <si>
-    <t>Invalid class key: notakey</t>
-  </si>
-  <si>
-    <t>The messages are shown verbatim: Select student or teacher under an empty Role, Enter a valid class key under an invalid Class key, and Add a teacher’s email under an empty Email on a teacher row.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. All three captured verbatim live 2026-08-24 from a restored draft. Add a teacher’s email confirms the form does distinguish the teacher case even though its help copy does not.</t>
-  </si>
-  <si>
-    <t>TST_STFB_TC_11</t>
-  </si>
-  <si>
-    <t>Verify translated text is shown when the form upload error dialog is raised</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Trigger the form upload error state.
-2. Read the dialog heading, body and close control.</t>
-  </si>
-  <si>
-    <t>Expected: the dialog reads Form not uploaded / An unexpected error occured. Please try again. / Close — the strings the product already ships. Actual (verified in the pre-rendered DOM, 2026-08-24): it renders three raw translation keys — ADMIN.LEARNER.ADULT_INVITE.FORM_UPLOAD_ERROR_HEADING as the heading, ADMIN.LEARNER.ADULT_INVITE.FORM_UPLOAD_ERROR_INFO as the body and ADMIN.LEARNER.ADULT_INVITE.FORM_UPLOAD_ERROR_CLOSE as the close button.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Expected-versus-actual. ROOT CAUSE established from the admin bundle 2026-08-24: the modal is #existingChildFormUploadErrorModal, a component reused from the add-existing-children CSV flow, but on this page it looks its copy up under ADMIN.LEARNER.ADULT_INVITE. The FORM_UPLOAD_ERROR_* strings are defined ONLY under ADMIN.LEARNER.EXISTING_CHILD and ADMIN.LEARNER.BULK_ACTIVATION (in both en and es) — the ADULT_INVITE block exists but does not define them, so ngx-translate falls back to printing the key. Changing site language does not help; Spanish has the same gap. Control test: the same dialog on the add-existing-children CSV screen renders correctly, which is why this has gone unnoticed. Note the correct string carries the known occured typo already recorded in admin-students-tab.md. Found by free-capture of the pre-rendered DOM (admin-shared.md A6) before the state was ever reached.</t>
+    <t>TST_STFP_TC_19</t>
+  </si>
+  <si>
+    <t>Verify a newly promoted administrator can actually open the admin console</t>
+  </si>
+  <si>
+    <t>#9 - Verify Grant admin rights</t>
+  </si>
+  <si>
+    <t>A disposable teacher account exists whose password the tester controls, currently without admin rights.</t>
+  </si>
+  <si>
+    <t>1. As an administrator, open the teacher's staff profile &gt; Manage account &gt; Grant admin rights and confirm. 2. Verify the role now reads Administrator/Teacher. 3. Sign out. 4. Sign in as that user. 5. Open the school and confirm the admin console and its tabs are reachable.</t>
+  </si>
+  <si>
+    <t>Disposable teacher &lt;DISPOSABLE_STAFF_ACCOUNT&gt; on the target school.</t>
+  </si>
+  <si>
+    <t>After the grant, the user can sign in and reach the admin console for that school, seeing the administrator tabs. [ASSUMED]</t>
+  </si>
+  <si>
+    <t>Added 2026-09-01 from the other team's TC_STF_009, whose step 3 is "log in as that user and confirm admin console access". Our TST_STFP_TC_10 stops at the role label changing in the UI - which a grant that updated the display but not the permission would also satisfy. This is the same shape as the Students password gap (TST_SPRF_TC_23): we verify the UI acknowledged the change, not that the change took effect. Mutates a real account - data-mutating suite, and revoke the rights afterwards as housekeeping.</t>
+  </si>
+  <si>
+    <t>TST_STFP_TC_20</t>
+  </si>
+  <si>
+    <t>Verify admin rights cannot be revoked from the only remaining administrator</t>
+  </si>
+  <si>
+    <t>#11 - Verify revoke admin rights</t>
+  </si>
+  <si>
+    <t>A school whose staff list contains exactly one administrator.</t>
+  </si>
+  <si>
+    <t>1. Open the sole administrator's staff profile &gt; Manage account. 2. Attempt Remove admin rights. 3. Read whether the control is unavailable or the action is blocked, and the message shown. 4. Re-read the role afterwards.</t>
+  </si>
+  <si>
+    <t>A school with a single administrator.</t>
+  </si>
+  <si>
+    <t>The action is prevented - the control is unavailable, or it is blocked with a message explaining the school must retain at least one administrator - and the role is unchanged afterwards. [ASSUMED]</t>
+  </si>
+  <si>
+    <t>Added 2026-09-01 from the other team's TC_STF_011_N1. No counterpart existed anywhere in our register. Related but distinct from TST_STFP_TC_14, which checks an administrator can reach Remove admin rights on their own profile - this one checks what happens when doing so would leave the school with none.</t>
   </si>
   <si>
     <t>Blocked</t>
   </si>
   <si>
-    <t>Blocked at design time — the dialog is present in the pre-rendered DOM but the condition that raises it has not been reproduced, so the case cannot be executed end to end. Root cause is known (missing ADULT_INVITE translation keys — see Remarks). Unblock: force the invitation form upload to fail — DevTools &gt; Network &gt; block the upload request, or go offline mid-upload — and confirm which of the three error modals is raised; if it is #existingChildFormUploadErrorModal rather than #errorFileUploadModal or #somethingWentWrongModal, the case is runnable.</t>
+    <t>Blocked at design time (skill rule 4): the precondition is a school with exactly one administrator. 3 July Test School 1 is shared and has several, and reducing it to one would break other suites. Unblock with a dedicated single-admin school.</t>
   </si>
   <si>
     <t>BLOCKED - see Comments for the blocker and its unblock route</t>
-  </si>
-  <si>
-    <t>TST_STFB_TC_12</t>
-  </si>
-  <si>
-    <t>Verify the browser tab title names the correct area when the invitation form is opened from the Staff tab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click Manage staff &gt; Add new teachers to classes.
-2. Read the browser tab title.</t>
-  </si>
-  <si>
-    <t>Expected: a title naming staff or the invitation form. Actual (verified live 2026-08-24): the tab reads Students | Cambridge One, even though the page was reached from the Staff tab and is headed Invite students and teachers.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Expected-versus-actual, low severity. Consistent with TST_STFB_TC_4 — the shared invite form is presented as a students screen throughout. Group both with the product owner as one copy/labelling issue rather than two.</t>
-  </si>
-  <si>
-    <t>TST_STFP_TC_19</t>
-  </si>
-  <si>
-    <t>Verify a newly promoted administrator can actually open the admin console</t>
-  </si>
-  <si>
-    <t>#9 - Verify Grant admin rights</t>
-  </si>
-  <si>
-    <t>A disposable teacher account exists whose password the tester controls, currently without admin rights.</t>
-  </si>
-  <si>
-    <t>1. As an administrator, open the teacher's staff profile &gt; Manage account &gt; Grant admin rights and confirm. 2. Verify the role now reads Administrator/Teacher. 3. Sign out. 4. Sign in as that user. 5. Open the school and confirm the admin console and its tabs are reachable.</t>
-  </si>
-  <si>
-    <t>Disposable teacher &lt;DISPOSABLE_STAFF_ACCOUNT&gt; on the target school.</t>
-  </si>
-  <si>
-    <t>After the grant, the user can sign in and reach the admin console for that school, seeing the administrator tabs. [ASSUMED]</t>
-  </si>
-  <si>
-    <t>Added 2026-09-01 from the other team's TC_STF_009, whose step 3 is "log in as that user and confirm admin console access". Our TST_STFP_TC_10 stops at the role label changing in the UI - which a grant that updated the display but not the permission would also satisfy. This is the same shape as the Students password gap (TST_SPRF_TC_23): we verify the UI acknowledged the change, not that the change took effect. Mutates a real account - data-mutating suite, and revoke the rights afterwards as housekeeping.</t>
-  </si>
-  <si>
-    <t>TST_STFP_TC_20</t>
-  </si>
-  <si>
-    <t>Verify admin rights cannot be revoked from the only remaining administrator</t>
-  </si>
-  <si>
-    <t>#11 - Verify revoke admin rights</t>
-  </si>
-  <si>
-    <t>A school whose staff list contains exactly one administrator.</t>
-  </si>
-  <si>
-    <t>1. Open the sole administrator's staff profile &gt; Manage account. 2. Attempt Remove admin rights. 3. Read whether the control is unavailable or the action is blocked, and the message shown. 4. Re-read the role afterwards.</t>
-  </si>
-  <si>
-    <t>A school with a single administrator.</t>
-  </si>
-  <si>
-    <t>The action is prevented - the control is unavailable, or it is blocked with a message explaining the school must retain at least one administrator - and the role is unchanged afterwards. [ASSUMED]</t>
-  </si>
-  <si>
-    <t>Added 2026-09-01 from the other team's TC_STF_011_N1. No counterpart existed anywhere in our register. Related but distinct from TST_STFP_TC_14, which checks an administrator can reach Remove admin rights on their own profile - this one checks what happens when doing so would leave the school with none.</t>
-  </si>
-  <si>
-    <t>Blocked at design time (skill rule 4): the precondition is a school with exactly one administrator. 3 July Test School 1 is shared and has several, and reducing it to one would break other suites. Unblock with a dedicated single-admin school.</t>
   </si>
 </sst>
 </file>
@@ -1655,7 +1319,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P58"/>
+  <dimension ref="A1:P41"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -1725,7 +1389,7 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>16</v>
@@ -1775,7 +1439,7 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>30</v>
@@ -1784,178 +1448,178 @@
         <v>31</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F3" s="3" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N3" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O3" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="P3" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="F4" s="3" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N4" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O4" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="P4" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="I5" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="L5" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N5" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O5" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="P5" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="K6" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="L6" s="3" t="s">
         <v>26</v>
@@ -1975,87 +1639,87 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="K7" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="I7" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="L7" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N7" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O7" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="P7" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="K8" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>26</v>
@@ -2075,137 +1739,137 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>21</v>
+        <v>74</v>
       </c>
       <c r="H9" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="K9" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O9" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="P9" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>21</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>81</v>
       </c>
       <c r="I10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J10" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="K10" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>84</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O10" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="P10" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>75</v>
-      </c>
       <c r="E11" s="3" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H11" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="K11" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="L11" s="3" t="s">
         <v>26</v>
@@ -2225,19 +1889,19 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>94</v>
+        <v>19</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>20</v>
@@ -2246,295 +1910,295 @@
         <v>21</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>98</v>
+        <v>57</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O12" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="P12" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="L13" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O13" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="P13" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O14" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="P14" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>114</v>
+        <v>86</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O15" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="P15" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>114</v>
+        <v>86</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="L16" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N16" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O16" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="P16" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>114</v>
+        <v>86</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="L17" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N17" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O17" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="P17" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>19</v>
@@ -2543,189 +2207,189 @@
         <v>20</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="L18" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O18" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="P18" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>134</v>
+        <v>21</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="L19" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N19" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O19" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="P19" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>23</v>
+        <v>134</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>23</v>
+        <v>109</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O20" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="P20" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
+        <v>26</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="G21" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="K21" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H21" s="3" t="s">
+      <c r="L21" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M21" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J21" s="3" t="s">
+      <c r="N21" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="O21" t="s">
         <v>145</v>
       </c>
-      <c r="K21" s="3" t="s">
+      <c r="P21" t="s">
         <v>146</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O21" t="s">
-        <v>38</v>
-      </c>
-      <c r="P21" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>147</v>
@@ -2734,28 +2398,28 @@
         <v>148</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>114</v>
+        <v>149</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>149</v>
+        <v>21</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>150</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>23</v>
+        <v>151</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>26</v>
@@ -2770,21 +2434,21 @@
         <v>28</v>
       </c>
       <c r="P22" t="s">
-        <v>29</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>19</v>
@@ -2793,39 +2457,39 @@
         <v>20</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>157</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>23</v>
+        <v>158</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>159</v>
+        <v>109</v>
       </c>
       <c r="L23" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N23" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O23" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="P23" t="s">
-        <v>39</v>
+        <v>154</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>160</v>
@@ -2834,157 +2498,157 @@
         <v>161</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>23</v>
+        <v>164</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O24" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="P24" t="s">
-        <v>39</v>
+        <v>154</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>21</v>
+        <v>170</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>57</v>
+        <v>172</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>137</v>
+        <v>174</v>
       </c>
       <c r="L25" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N25" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O25" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="P25" t="s">
-        <v>39</v>
+        <v>154</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>155</v>
-      </c>
       <c r="E26" s="3" t="s">
-        <v>94</v>
+        <v>19</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>21</v>
+        <v>177</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>23</v>
+        <v>179</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="L26" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>27</v>
+        <v>144</v>
       </c>
       <c r="N26" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O26" t="s">
-        <v>28</v>
+        <v>145</v>
       </c>
       <c r="P26" t="s">
-        <v>29</v>
+        <v>146</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>19</v>
@@ -2993,19 +2657,19 @@
         <v>20</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>181</v>
+        <v>109</v>
       </c>
       <c r="L27" s="3" t="s">
         <v>26</v>
@@ -3017,24 +2681,24 @@
         <v>26</v>
       </c>
       <c r="O27" t="s">
-        <v>182</v>
+        <v>28</v>
       </c>
       <c r="P27" t="s">
-        <v>183</v>
+        <v>154</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>184</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>186</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>19</v>
@@ -3043,48 +2707,48 @@
         <v>20</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>21</v>
+        <v>189</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>188</v>
+        <v>158</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L28" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N28" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O28" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="P28" t="s">
-        <v>191</v>
+        <v>154</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>19</v>
@@ -3093,48 +2757,48 @@
         <v>20</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>21</v>
+        <v>195</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>137</v>
+        <v>199</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>37</v>
+        <v>144</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O29" t="s">
-        <v>38</v>
+        <v>145</v>
       </c>
       <c r="P29" t="s">
-        <v>191</v>
+        <v>146</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>19</v>
@@ -3143,19 +2807,19 @@
         <v>20</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="L30" s="3" t="s">
         <v>26</v>
@@ -3170,42 +2834,42 @@
         <v>28</v>
       </c>
       <c r="P30" t="s">
-        <v>29</v>
+        <v>154</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>21</v>
+        <v>209</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>206</v>
+        <v>57</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="L31" s="3" t="s">
         <v>26</v>
@@ -3220,171 +2884,171 @@
         <v>28</v>
       </c>
       <c r="P31" t="s">
-        <v>29</v>
+        <v>154</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>94</v>
+        <v>19</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>21</v>
+        <v>215</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>27</v>
+        <v>144</v>
       </c>
       <c r="N32" s="3" t="s">
-        <v>215</v>
+        <v>26</v>
       </c>
       <c r="O32" t="s">
-        <v>28</v>
+        <v>145</v>
       </c>
       <c r="P32" t="s">
-        <v>29</v>
+        <v>146</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
+        <v>43</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E33" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>21</v>
+        <v>209</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>220</v>
+        <v>57</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L33" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N33" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O33" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="P33" t="s">
-        <v>191</v>
+        <v>154</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>226</v>
+        <v>57</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L34" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>27</v>
+        <v>144</v>
       </c>
       <c r="N34" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O34" t="s">
-        <v>28</v>
+        <v>145</v>
       </c>
       <c r="P34" t="s">
-        <v>29</v>
+        <v>146</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>19</v>
@@ -3393,13 +3057,13 @@
         <v>20</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>234</v>
+        <v>57</v>
       </c>
       <c r="J35" s="3" t="s">
         <v>235</v>
@@ -3411,21 +3075,21 @@
         <v>26</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>37</v>
+        <v>144</v>
       </c>
       <c r="N35" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O35" t="s">
-        <v>38</v>
+        <v>145</v>
       </c>
       <c r="P35" t="s">
-        <v>191</v>
+        <v>146</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>237</v>
@@ -3434,13 +3098,13 @@
         <v>238</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>239</v>
@@ -3449,92 +3113,92 @@
         <v>240</v>
       </c>
       <c r="I36" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J36" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="J36" s="3" t="s">
+      <c r="K36" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="K36" s="3" t="s">
-        <v>243</v>
-      </c>
       <c r="L36" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>27</v>
+        <v>144</v>
       </c>
       <c r="N36" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O36" t="s">
-        <v>182</v>
+        <v>145</v>
       </c>
       <c r="P36" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="B37" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>245</v>
-      </c>
       <c r="D37" s="3" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="G37" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="K37" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="H37" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="K37" s="3" t="s">
-        <v>137</v>
-      </c>
       <c r="L37" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>37</v>
+        <v>144</v>
       </c>
       <c r="N37" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O37" t="s">
-        <v>38</v>
+        <v>145</v>
       </c>
       <c r="P37" t="s">
-        <v>191</v>
+        <v>146</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B38" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>250</v>
-      </c>
       <c r="D38" s="3" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>19</v>
@@ -3543,13 +3207,13 @@
         <v>20</v>
       </c>
       <c r="G38" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="H38" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="H38" s="3" t="s">
+      <c r="I38" s="3" t="s">
         <v>252</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>195</v>
       </c>
       <c r="J38" s="3" t="s">
         <v>253</v>
@@ -3561,21 +3225,21 @@
         <v>26</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>37</v>
+        <v>144</v>
       </c>
       <c r="N38" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O38" t="s">
-        <v>38</v>
+        <v>145</v>
       </c>
       <c r="P38" t="s">
-        <v>191</v>
+        <v>146</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>255</v>
@@ -3584,10 +3248,10 @@
         <v>256</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>20</v>
@@ -3611,21 +3275,21 @@
         <v>26</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>27</v>
+        <v>144</v>
       </c>
       <c r="N39" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O39" t="s">
-        <v>182</v>
+        <v>145</v>
       </c>
       <c r="P39" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>262</v>
@@ -3634,943 +3298,93 @@
         <v>263</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L40" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>27</v>
+        <v>144</v>
       </c>
       <c r="N40" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="O40" t="s">
-        <v>28</v>
-      </c>
-      <c r="P40" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O40" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="P40" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>199</v>
+        <v>273</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>23</v>
+        <v>275</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="L41" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>37</v>
+        <v>278</v>
       </c>
       <c r="N41" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O41" t="s">
-        <v>38</v>
-      </c>
-      <c r="P41" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A42" s="3">
-        <v>41</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="H42" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="O41" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="K42" s="3" t="s">
+      <c r="P41" s="3" t="s">
         <v>280</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O42" t="s">
-        <v>38</v>
-      </c>
-      <c r="P42" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A43" s="3">
-        <v>42</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N43" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O43" t="s">
-        <v>182</v>
-      </c>
-      <c r="P43" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A44" s="3">
-        <v>43</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M44" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="N44" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O44" t="s">
-        <v>38</v>
-      </c>
-      <c r="P44" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A45" s="3">
-        <v>44</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O45" t="s">
-        <v>182</v>
-      </c>
-      <c r="P45" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A46" s="3">
-        <v>45</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M46" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N46" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O46" t="s">
-        <v>182</v>
-      </c>
-      <c r="P46" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A47" s="3">
-        <v>46</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O47" t="s">
-        <v>182</v>
-      </c>
-      <c r="P47" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A48" s="3">
-        <v>47</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M48" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N48" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O48" t="s">
-        <v>182</v>
-      </c>
-      <c r="P48" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A49" s="3">
-        <v>48</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M49" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N49" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O49" t="s">
-        <v>182</v>
-      </c>
-      <c r="P49" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A50" s="3">
-        <v>49</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J50" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="K50" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="L50" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M50" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N50" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O50" t="s">
-        <v>28</v>
-      </c>
-      <c r="P50" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A51" s="3">
-        <v>50</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J51" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="K51" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="L51" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M51" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N51" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O51" t="s">
-        <v>28</v>
-      </c>
-      <c r="P51" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A52" s="3">
-        <v>51</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N52" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O52" t="s">
-        <v>28</v>
-      </c>
-      <c r="P52" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A53" s="3">
-        <v>52</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="I53" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="J53" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="K53" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="L53" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M53" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N53" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O53" t="s">
-        <v>182</v>
-      </c>
-      <c r="P53" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A54" s="3">
-        <v>53</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="K54" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="L54" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M54" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N54" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O54" t="s">
-        <v>28</v>
-      </c>
-      <c r="P54" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A55" s="3">
-        <v>54</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="I55" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J55" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="K55" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="L55" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M55" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="N55" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="O55" t="s">
-        <v>359</v>
-      </c>
-      <c r="P55" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A56" s="3">
-        <v>55</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G56" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H56" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="I56" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J56" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="K56" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="L56" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M56" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N56" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O56" t="s">
-        <v>28</v>
-      </c>
-      <c r="P56" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="3">
-        <v>56</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N57" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="P57" s="3" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="3">
-        <v>57</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>361</v>
       </c>
     </row>
   </sheetData>

--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Staff/AdminApp_Staff_tab_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Staff/AdminApp_Staff_tab_test_cases.xlsx
@@ -102,7 +102,7 @@
     <t>Automated</t>
   </si>
   <si>
-    <t>Suite: adminStaffTab | Not executed in this audit - status carried over, treat as unverified</t>
+    <t>Suite: adminStaffTab | 2026-09-16: Pass across 2 runs</t>
   </si>
   <si>
     <t>TST_STFL_TC_3</t>
@@ -510,7 +510,7 @@
     <t>The row itself is the menu toggle — the whole row is a button with data-toggle="dropdown", and the menu holds exactly ONE item, View profile. There is no "Activate course materials" item as there is on the Students tab. teacher17aug2026@mailsac.com is the team-nominated teacher fixture for this school [confirmed with the team 2026-08-24].</t>
   </si>
   <si>
-    <t>Suite: adminStaffProfile | Not executed in this audit - status carried over, treat as unverified</t>
+    <t>Suite: adminStaffProfile | 2026-09-16: Pass across 2 runs</t>
   </si>
   <si>
     <t>TST_STFP_TC_2</t>

--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Staff/AdminApp_Staff_tab_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Staff/AdminApp_Staff_tab_test_cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="281">
   <si>
     <t>S.No.</t>
   </si>
@@ -61,13 +61,13 @@
     <t>Automation Evidence</t>
   </si>
   <si>
-    <t>TST_STFL_TC_1</t>
-  </si>
-  <si>
-    <t>Verify the Staff tab loads with all expected components when the school is opened by an administrator</t>
-  </si>
-  <si>
-    <t>— Staff tab load (added, not in source)</t>
+    <t>TST_STFL_TC_2</t>
+  </si>
+  <si>
+    <t>Verify matching staff are returned when a full first name is searched</t>
+  </si>
+  <si>
+    <t>#1 — Verify search by first name</t>
   </si>
   <si>
     <t>Positive</t>
@@ -77,41 +77,6 @@
   </si>
   <si>
     <t>Logged in as school admin testt1@mailsac.com on thor. School FCN-CHZ-PDA ("3 July Test School 1") opened from "My school accounts" BY KEY. Staff tab open at /admin/admin/org_perf_testschool_1/staff.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open school "3 July Test School 1" by key FCN-CHZ-PDA from "My school accounts".
-2. Click "Staff" in the left navigation.
-3. Observe the page.</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>The URL is /admin/admin/org_&lt;slug&gt;/staff and the browser tab reads "Staff | Cambridge One". The page shows: heading Staff (N); a search box placeholder Search by first name, last name or email with a Search button; a Manage staff menu; a collapsed User guide toggle; a sortable table headed Last name | First name | Email address | Role, sorted by Last name ascending; up to 20 staff rows; and Load more ... when more than 20 staff exist.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Column set differs from the Students tab — there is a Role column and there is NO row-selection checkbox, no N Selected counter and no bulk "Remove from school account" on the list. Role values seen: Teacher, Administrator/Teacher.</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Not Run</t>
-  </si>
-  <si>
-    <t>Excluded - Phase 1</t>
-  </si>
-  <si>
-    <t>Out of Phase 1 automation scope.</t>
-  </si>
-  <si>
-    <t>TST_STFL_TC_2</t>
-  </si>
-  <si>
-    <t>Verify matching staff are returned when a full first name is searched</t>
-  </si>
-  <si>
-    <t>#1 — Verify search by first name</t>
   </si>
   <si>
     <t xml:space="preserve">1. Type teacher19oct in the search box.
@@ -126,6 +91,9 @@
   </si>
   <si>
     <t>Search covers first name, last name and email from the single box.</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>Pass</t>
@@ -183,26 +151,6 @@
     <t>Case-preserving echo is confirmed behaviour on the sibling Students tab and re-observed here.</t>
   </si>
   <si>
-    <t>TST_STFL_TC_5</t>
-  </si>
-  <si>
-    <t>Verify the list is unchanged when a search term is typed but the Search button is not clicked</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Type gg in the search box.
-2. Do NOT click Search. Wait 3 s.
-3. Observe the heading and rows.</t>
-  </si>
-  <si>
-    <t>gg</t>
-  </si>
-  <si>
-    <t>The list is not filtered — the heading still reads Staff (N) and the same rows are shown. Search is submit-driven, not live.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-24: typing alone left the heading at Staff (23).</t>
-  </si>
-  <si>
     <t>TST_STFL_TC_6</t>
   </si>
   <si>
@@ -225,25 +173,6 @@
     <t>Verified live 2026-08-24 — exactly these two rows returned.</t>
   </si>
   <si>
-    <t>TST_STFL_TC_7</t>
-  </si>
-  <si>
-    <t>Verify the full staff list is restored when Clear is clicked after a search</t>
-  </si>
-  <si>
-    <t>Logged in as school admin testt1@mailsac.com on thor. School FCN-CHZ-PDA ("3 July Test School 1") opened from "My school accounts" BY KEY. Staff tab open at /admin/admin/org_perf_testschool_1/staff. A search for gg has been submitted.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click Clear in the search banner.
-2. Observe the heading, the search box and the rows.</t>
-  </si>
-  <si>
-    <t>The banner is replaced by the Staff (N) count heading, the search box is emptied, the first page of 20 staff is shown again and Load more ... reappears.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-24: heading returned to Staff (23), box empty, 20 rows, Load more present.</t>
-  </si>
-  <si>
     <t>TST_STFL_TC_8</t>
   </si>
   <si>
@@ -263,6 +192,9 @@
     <t>Exactly one row is listed — gg | testteacher18 | testteacher18oct@mailsac.com | Administrator/Teacher — and the banner echoes the full address.</t>
   </si>
   <si>
+    <t>—</t>
+  </si>
+  <si>
     <t>TST_STFL_TC_9</t>
   </si>
   <si>
@@ -280,28 +212,6 @@
   </si>
   <si>
     <t>Nine Perf Test rows carried @yopmail.com at capture; do not assert the number.</t>
-  </si>
-  <si>
-    <t>TST_STFL_TC_10</t>
-  </si>
-  <si>
-    <t>Verify the search banner state is entered and every staff member returned when the term is whitespace only</t>
-  </si>
-  <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Type three spaces in the search box.
-2. Click Search.</t>
-  </si>
-  <si>
-    <t>Three space characters</t>
-  </si>
-  <si>
-    <t>The term is trimmed to nothing, but the page still enters the search banner state — the count heading is replaced by Showing search results for . with Clear — and every staff member is returned. [ASSUMED] — not exercised live on the Staff tab; this is the confirmed Students-tab behaviour.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. [ASSUMED]. Entering the banner state on an empty term is arguably wrong; it is recorded as an observation, not a defect case. Confirm during Phase 1.</t>
   </si>
   <si>
     <t>TST_STFL_TC_11</t>
@@ -481,25 +391,6 @@
   </si>
   <si>
     <t>Verified live 2026-08-24. Same collation rule as the Classes and Students tabs (admin-shared.md §A4).</t>
-  </si>
-  <si>
-    <t>TST_STFL_TC_21</t>
-  </si>
-  <si>
-    <t>Verify the list returns to the first page of 20 when the sort column is changed after Load more</t>
-  </si>
-  <si>
-    <t>Logged in as school admin testt1@mailsac.com on thor. School FCN-CHZ-PDA ("3 July Test School 1") opened from "My school accounts" BY KEY. Staff tab open at /admin/admin/org_perf_testschool_1/staff. Load more ... has been clicked so the full list is rendered and the link has gone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click any column header to change the sort.
-2. Count the rendered rows and look for Load more ....</t>
-  </si>
-  <si>
-    <t>The list is truncated back to the first 20 rows in the new order and Load more ... is present again.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-24 — sorting resets pagination.</t>
   </si>
   <si>
     <t>TST_STFL_TC_23</t>
@@ -553,25 +444,10 @@
 4. Look for Load more ... again.</t>
   </si>
   <si>
+    <t>gg</t>
+  </si>
+  <si>
     <t>Load more ... is absent while the two-row result set is shown, and reappears after Clear restores the full list.</t>
-  </si>
-  <si>
-    <t>TST_STFL_TC_26</t>
-  </si>
-  <si>
-    <t>Verify the heading count matches the number of staff rows when the whole list has been loaded</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Read the count in the heading Staff (N).
-2. Click Load more ... until it is removed from the page.
-3. Count the rendered staff rows.
-4. Compare the two numbers.</t>
-  </si>
-  <si>
-    <t>Expected: the number of rendered rows equals the heading count. Actual (verified live 2026-08-24): the heading read Staff (23) but the exhausted list rendered only 21 unique rows — a shortfall of 2 with Load more ... already removed.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Expected-versus-actual — a real defect, confirmed with the team 2026-08-24. The count is NOT explained by pending invitations: the team confirmed that Staff (N) increments only when an invited teacher ACCEPTS, so invited-but-not-joined staff are not counted. The 2-row shortfall is therefore unexplained. It may be specific to this school's data. Because the school is shared, automate this as "heading count equals rendered row count", never as the literal numbers 23 and 21 — and expect this case to FAIL on FCN-CHZ-PDA until the data or the defect is fixed.</t>
   </si>
   <si>
     <t>TST_STFL_TC_27</t>
@@ -602,6 +478,9 @@
     <t>Sends real email and creates a real account — mailsac/yopmail addresses only, prefix AutoStaff_. The count timing is now confirmed (acceptance, not invitation), so this case is no longer [ASSUMED] on that point; what remains unverified is the end-to-end run itself. Note TST_STFL_TC_26: the heading count and the rendered rows already disagree by 2 on this school, so assert the DELTA on the count, not the row total.</t>
   </si>
   <si>
+    <t>Not Run</t>
+  </si>
+  <si>
     <t>Not Automated</t>
   </si>
   <si>
@@ -650,69 +529,6 @@
     <t>The profile shows the heading gg, testteacher18 and the role line reads Administrator/Teacher, matching the Role column on the list.</t>
   </si>
   <si>
-    <t>TST_STFP_TC_3</t>
-  </si>
-  <si>
-    <t>Verify the Staff tab is restored when Back is clicked on a staff profile</t>
-  </si>
-  <si>
-    <t>Logged in as school admin testt1@mailsac.com on thor. School FCN-CHZ-PDA ("3 July Test School 1") opened from "My school accounts" BY KEY. Staff tab open at /admin/admin/org_perf_testschool_1/staff. A staff profile has been opened via the row action menu &gt; "View profile" (the profile URL is NOT deep-linkable, so a staff profile cannot be reached directly).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click Back.
-2. Observe the page.</t>
-  </si>
-  <si>
-    <t>The Staff tab is shown again at /admin/admin/org_&lt;slug&gt;/staff, in its default state — heading Staff (N), sorted by Last name ascending, first page of 20 rows.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-24. Any search or sort applied before opening the profile is NOT preserved on return — check this explicitly during Phase 1 if a test depends on it.</t>
-  </si>
-  <si>
-    <t>TST_STFP_TC_4</t>
-  </si>
-  <si>
-    <t>Verify an empty-state message is shown when the staff member belongs to no classes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open the profile of teacher17aug2026@mailsac.com, who teaches no classes.
-2. Read the classes section.</t>
-  </si>
-  <si>
-    <t>Teacher with no classes: teacher17aug2026@mailsac.com</t>
-  </si>
-  <si>
-    <t>The classes section shows No class with Your classes will appear here and an Add classes control, instead of a Classes (N) list.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-24 on two separate profiles. [ASSUMED] that teacher17aug2026@mailsac.com also has no classes — confirm on the first run and swap the fixture if it does.</t>
-  </si>
-  <si>
-    <t>TST_STFP_TC_6</t>
-  </si>
-  <si>
-    <t>Verify a user-visible error is shown and the page stays usable when the profile request fails</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Locate the row Perf Test | tch_L_20240705-095330_1_FCN-CHZ-PDA | ...@yopmail.com | Teacher.
-2. Open its action menu and click View profile.
-3. Observe the page for any error message.
-4. Without reloading, try to click a different staff row.
-5. Check the network panel for the getUserDetailWithClasses response.</t>
-  </si>
-  <si>
-    <t>Known-bad data fixture: tch_L_20240705-095330_1_FCN-CHZ-PDA@yopmail.com</t>
-  </si>
-  <si>
-    <t>Expected: the user sees an error explaining that the profile could not be loaded, and the Staff list remains usable — a different row can still be opened. Actual (verified live 2026-08-24): nothing is shown at all, the app silently stays on the list, and the #loader-container overlay is left visible so every subsequent row click is intercepted until the page is reloaded.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Expected-versus-actual, scoped to CLIENT-SIDE ERROR HANDLING only. The underlying HTTP 500 from getUserDetailWithClasses is a KNOWN DATA ISSUE on this one account — confirmed with the team 2026-08-24 — and is NOT part of this case; do not raise it as a product defect. What remains product-side is that any 500 produces no message and a stuck overlay. The 500 account is retained deliberately as the trigger fixture; teacher17aug2026@mailsac.com is the healthy teacher fixture used elsewhere.</t>
-  </si>
-  <si>
-    <t>HTTP 500 confirmed as a known data issue with the team, 2026-08-24. Case narrowed to the missing error handling and the stuck loading overlay.</t>
-  </si>
-  <si>
     <t>TST_STFP_TC_7</t>
   </si>
   <si>
@@ -734,25 +550,6 @@
   </si>
   <si>
     <t>Verified live 2026-08-24. Each listed class is a real link (user-profile-6-&lt;index&gt;). Contrast with the student profile, where the umbrella name is plain text with no link — do not assume the two profiles behave alike. Crossing from admin to class is a full page load, not an Angular route change; budget for it.</t>
-  </si>
-  <si>
-    <t>TST_STFP_TC_8</t>
-  </si>
-  <si>
-    <t>Verify each listed class shows its dates, join date and class key on a staff profile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open the profile of testt1@mailsac.com.
-2. Read the Classes (3) section.</t>
-  </si>
-  <si>
-    <t>Staff with classes: testt1@mailsac.com</t>
-  </si>
-  <si>
-    <t>The heading reads Classes (N) and each entry shows the class name, its date range, Date joined: &lt;date&gt;, Class key: &lt;key&gt; and the course material name — e.g. A11y test / Jul 11, 2025 - Jul 10, 2026 / Date joined: Jul 11, 2025 / Class key: iCmL-9Y8J / Collaborate 3 (NLP).</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-24. Launching an ended class shows the class page with the banner As this class ended over a month ago, you can no longer reactivate it. and a Class ended status.</t>
   </si>
   <si>
     <t>TST_STFP_TC_9</t>
@@ -865,29 +662,6 @@
     <t>[ASSUMED]. Mutating — run only against an account this suite created.</t>
   </si>
   <si>
-    <t>TST_STFP_TC_14</t>
-  </si>
-  <si>
-    <t>Verify the administrator can reach Remove admin rights on their own staff profile</t>
-  </si>
-  <si>
-    <t>Logged in as school admin testt1@mailsac.com on thor. School FCN-CHZ-PDA ("3 July Test School 1") opened from "My school accounts" BY KEY. Staff tab open at /admin/admin/org_perf_testschool_1/staff. The profile of the signed-in administrator testt1@mailsac.com is open.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click Manage account.
-2. Read the menu items.
-3. Do NOT confirm.</t>
-  </si>
-  <si>
-    <t>Own account: testt1@mailsac.com</t>
-  </si>
-  <si>
-    <t>Remove admin rights and Remove from school account are both offered on the administrator's own profile — the product does not exclude the signed-in user from either action.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-24 (menu inspected only). Never confirm either action on this account — it is the login used by every admin suite, and self-revoking would lock the whole programme out. Worth raising: should self-revocation and self-removal be prevented, or at least warned about?</t>
-  </si>
-  <si>
     <t>TST_STFP_TC_15</t>
   </si>
   <si>
@@ -895,6 +669,9 @@
   </si>
   <si>
     <t>#10 — Verify remove from school account</t>
+  </si>
+  <si>
+    <t>Logged in as school admin testt1@mailsac.com on thor. School FCN-CHZ-PDA ("3 July Test School 1") opened from "My school accounts" BY KEY. Staff tab open at /admin/admin/org_perf_testschool_1/staff. A staff profile has been opened via the row action menu &gt; "View profile" (the profile URL is NOT deep-linkable, so a staff profile cannot be reached directly).</t>
   </si>
   <si>
     <t xml:space="preserve">1. Click Manage account &gt; Remove from school account.
@@ -1069,63 +846,6 @@
     <t>Dialog copy captured verbatim from the pre-rendered DOM, 2026-08-24; the send itself was not performed. Sends real email — mailsac/yopmail addresses only, prefix AutoStaff_. Two copy defects visible in this dialog: school Account (stray capital A) and the missing space after each class.</t>
   </si>
   <si>
-    <t>TST_STFB_TC_5</t>
-  </si>
-  <si>
-    <t>Verify the bulk row actions are unavailable when no rows are selected</t>
-  </si>
-  <si>
-    <t>The invitation form is open with no row checkboxes ticked.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Confirm the counter reads 0 Selected.
-2. Observe Add role, + Add class key and Remove.</t>
-  </si>
-  <si>
-    <t>All three bulk actions are presented as unavailable while 0 Selected is shown.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-24. Automation trap: these three controls carry no qid and are disabled by the CSS class disable (not disabled, and with no native disabled property). Resolve them by their text and assert on the class.</t>
-  </si>
-  <si>
-    <t>TST_STFB_TC_6</t>
-  </si>
-  <si>
-    <t>Verify a previously saved draft is restored when the invitation form is re-opened</t>
-  </si>
-  <si>
-    <t>A draft invitation has previously been entered on this form and left unsent.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open Manage staff &gt; Add new teachers to classes.
-2. Observe the grid rows and the area above it.</t>
-  </si>
-  <si>
-    <t>The form is not empty — the previously entered rows are restored, a Saved &lt;age&gt; indicator is shown (e.g. Saved 30+ days ago), the submit button counts the restored rows, and any validation messages on those rows are already displayed.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-24 — the form opened showing Saved 30+ days ago, four restored rows and live validation messages. Same auto-save/restore behaviour as the Create new classes form (admin-shared.md §A4). A test that assumes an empty form will fail, and the draft is shared state on a shared school — do not assume your own suite wrote it.</t>
-  </si>
-  <si>
-    <t>TST_STFB_TC_7</t>
-  </si>
-  <si>
-    <t>Verify the submit button is unavailable while any invitation row is incomplete</t>
-  </si>
-  <si>
-    <t>The invitation form is open with at least one row missing a required value.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Leave a row without a role or without a valid class key.
-2. Observe the Send N invites button.</t>
-  </si>
-  <si>
-    <t>The Send N invites button is unavailable while any row fails validation.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-24 — the button was both natively disabled and carried the disabled class in this state.</t>
-  </si>
-  <si>
     <t>TST_STFB_TC_9</t>
   </si>
   <si>
@@ -1150,117 +870,61 @@
     <t>Fixture written 2026-08-24 from the real downloaded template, headers verified. It omits the template example row and uses class key wLE3-zTx6 (AutoClass_CreateOnly, active Aug 24 2026 - Sep 15 2026) — an auto-created class this programme already owns. If that class has been swept, substitute any active class key from the Classes tab. [ASSUMED] whether the Role value must be exactly Teacher (the template example uses Student) and whether the example row must be removed before upload — resolve both on the first run. During upload the product shows Please wait, this may takea few minutes — note the missing space in takea, a copy defect to raise. On failure it shows Sorry, your file could not be uploaded with the ptsupport@cambridge.org contact.</t>
   </si>
   <si>
-    <t>TST_STFB_TC_8</t>
-  </si>
-  <si>
-    <t>Verify per-field validation messages are shown when invitation rows are incomplete or invalid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Leave the Role cell of a populated row empty.
-2. Enter an invalid class key in another row.
-3. Leave the Email cell of a row that has a role empty.
-4. Read the messages under each cell.</t>
-  </si>
-  <si>
-    <t>Invalid class key: notakey</t>
-  </si>
-  <si>
-    <t>The messages are shown verbatim: Select student or teacher under an empty Role, Enter a valid class key under an invalid Class key, and Add a teacher’s email under an empty Email on a teacher row.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. All three captured verbatim live 2026-08-24 from a restored draft. Add a teacher’s email confirms the form does distinguish the teacher case even though its help copy does not.</t>
-  </si>
-  <si>
-    <t>TST_STFB_TC_11</t>
-  </si>
-  <si>
-    <t>Verify translated text is shown when the form upload error dialog is raised</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Trigger the form upload error state.
-2. Read the dialog heading, body and close control.</t>
-  </si>
-  <si>
-    <t>Expected: the dialog reads Form not uploaded / An unexpected error occured. Please try again. / Close — the strings the product already ships. Actual (verified in the pre-rendered DOM, 2026-08-24): it renders three raw translation keys — ADMIN.LEARNER.ADULT_INVITE.FORM_UPLOAD_ERROR_HEADING as the heading, ADMIN.LEARNER.ADULT_INVITE.FORM_UPLOAD_ERROR_INFO as the body and ADMIN.LEARNER.ADULT_INVITE.FORM_UPLOAD_ERROR_CLOSE as the close button.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Expected-versus-actual. ROOT CAUSE established from the admin bundle 2026-08-24: the modal is #existingChildFormUploadErrorModal, a component reused from the add-existing-children CSV flow, but on this page it looks its copy up under ADMIN.LEARNER.ADULT_INVITE. The FORM_UPLOAD_ERROR_* strings are defined ONLY under ADMIN.LEARNER.EXISTING_CHILD and ADMIN.LEARNER.BULK_ACTIVATION (in both en and es) — the ADULT_INVITE block exists but does not define them, so ngx-translate falls back to printing the key. Changing site language does not help; Spanish has the same gap. Control test: the same dialog on the add-existing-children CSV screen renders correctly, which is why this has gone unnoticed. Note the correct string carries the known occured typo already recorded in admin-students-tab.md. Found by free-capture of the pre-rendered DOM (admin-shared.md A6) before the state was ever reached.</t>
+    <t>TST_STFP_TC_19</t>
+  </si>
+  <si>
+    <t>Verify a newly promoted administrator can actually open the admin console</t>
+  </si>
+  <si>
+    <t>#9 - Verify Grant admin rights</t>
+  </si>
+  <si>
+    <t>A disposable teacher account exists whose password the tester controls, currently without admin rights.</t>
+  </si>
+  <si>
+    <t>1. As an administrator, open the teacher's staff profile &gt; Manage account &gt; Grant admin rights and confirm. 2. Verify the role now reads Administrator/Teacher. 3. Sign out. 4. Sign in as that user. 5. Open the school and confirm the admin console and its tabs are reachable.</t>
+  </si>
+  <si>
+    <t>Disposable teacher &lt;DISPOSABLE_STAFF_ACCOUNT&gt; on the target school.</t>
+  </si>
+  <si>
+    <t>After the grant, the user can sign in and reach the admin console for that school, seeing the administrator tabs. [ASSUMED]</t>
+  </si>
+  <si>
+    <t>Added 2026-09-01 from the other team's TC_STF_009, whose step 3 is "log in as that user and confirm admin console access". Our TST_STFP_TC_10 stops at the role label changing in the UI - which a grant that updated the display but not the permission would also satisfy. This is the same shape as the Students password gap (TST_SPRF_TC_23): we verify the UI acknowledged the change, not that the change took effect. Mutates a real account - data-mutating suite, and revoke the rights afterwards as housekeeping.</t>
+  </si>
+  <si>
+    <t>TST_STFP_TC_20</t>
+  </si>
+  <si>
+    <t>Verify admin rights cannot be revoked from the only remaining administrator</t>
+  </si>
+  <si>
+    <t>#11 - Verify revoke admin rights</t>
+  </si>
+  <si>
+    <t>A school whose staff list contains exactly one administrator.</t>
+  </si>
+  <si>
+    <t>1. Open the sole administrator's staff profile &gt; Manage account. 2. Attempt Remove admin rights. 3. Read whether the control is unavailable or the action is blocked, and the message shown. 4. Re-read the role afterwards.</t>
+  </si>
+  <si>
+    <t>A school with a single administrator.</t>
+  </si>
+  <si>
+    <t>The action is prevented - the control is unavailable, or it is blocked with a message explaining the school must retain at least one administrator - and the role is unchanged afterwards. [ASSUMED]</t>
+  </si>
+  <si>
+    <t>Added 2026-09-01 from the other team's TC_STF_011_N1. No counterpart existed anywhere in our register. Related but distinct from TST_STFP_TC_14, which checks an administrator can reach Remove admin rights on their own profile - this one checks what happens when doing so would leave the school with none.</t>
   </si>
   <si>
     <t>Blocked</t>
   </si>
   <si>
-    <t>Blocked at design time — the dialog is present in the pre-rendered DOM but the condition that raises it has not been reproduced, so the case cannot be executed end to end. Root cause is known (missing ADULT_INVITE translation keys — see Remarks). Unblock: force the invitation form upload to fail — DevTools &gt; Network &gt; block the upload request, or go offline mid-upload — and confirm which of the three error modals is raised; if it is #existingChildFormUploadErrorModal rather than #errorFileUploadModal or #somethingWentWrongModal, the case is runnable.</t>
+    <t>Blocked at design time (skill rule 4): the precondition is a school with exactly one administrator. 3 July Test School 1 is shared and has several, and reducing it to one would break other suites. Unblock with a dedicated single-admin school.</t>
   </si>
   <si>
     <t>BLOCKED - see Comments for the blocker and its unblock route</t>
-  </si>
-  <si>
-    <t>TST_STFB_TC_12</t>
-  </si>
-  <si>
-    <t>Verify the browser tab title names the correct area when the invitation form is opened from the Staff tab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click Manage staff &gt; Add new teachers to classes.
-2. Read the browser tab title.</t>
-  </si>
-  <si>
-    <t>Expected: a title naming staff or the invitation form. Actual (verified live 2026-08-24): the tab reads Students | Cambridge One, even though the page was reached from the Staff tab and is headed Invite students and teachers.</t>
-  </si>
-  <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Expected-versus-actual, low severity. Consistent with TST_STFB_TC_4 — the shared invite form is presented as a students screen throughout. Group both with the product owner as one copy/labelling issue rather than two.</t>
-  </si>
-  <si>
-    <t>TST_STFP_TC_19</t>
-  </si>
-  <si>
-    <t>Verify a newly promoted administrator can actually open the admin console</t>
-  </si>
-  <si>
-    <t>#9 - Verify Grant admin rights</t>
-  </si>
-  <si>
-    <t>A disposable teacher account exists whose password the tester controls, currently without admin rights.</t>
-  </si>
-  <si>
-    <t>1. As an administrator, open the teacher's staff profile &gt; Manage account &gt; Grant admin rights and confirm. 2. Verify the role now reads Administrator/Teacher. 3. Sign out. 4. Sign in as that user. 5. Open the school and confirm the admin console and its tabs are reachable.</t>
-  </si>
-  <si>
-    <t>Disposable teacher &lt;DISPOSABLE_STAFF_ACCOUNT&gt; on the target school.</t>
-  </si>
-  <si>
-    <t>After the grant, the user can sign in and reach the admin console for that school, seeing the administrator tabs. [ASSUMED]</t>
-  </si>
-  <si>
-    <t>Added 2026-09-01 from the other team's TC_STF_009, whose step 3 is "log in as that user and confirm admin console access". Our TST_STFP_TC_10 stops at the role label changing in the UI - which a grant that updated the display but not the permission would also satisfy. This is the same shape as the Students password gap (TST_SPRF_TC_23): we verify the UI acknowledged the change, not that the change took effect. Mutates a real account - data-mutating suite, and revoke the rights afterwards as housekeeping.</t>
-  </si>
-  <si>
-    <t>TST_STFP_TC_20</t>
-  </si>
-  <si>
-    <t>Verify admin rights cannot be revoked from the only remaining administrator</t>
-  </si>
-  <si>
-    <t>#11 - Verify revoke admin rights</t>
-  </si>
-  <si>
-    <t>A school whose staff list contains exactly one administrator.</t>
-  </si>
-  <si>
-    <t>1. Open the sole administrator's staff profile &gt; Manage account. 2. Attempt Remove admin rights. 3. Read whether the control is unavailable or the action is blocked, and the message shown. 4. Re-read the role afterwards.</t>
-  </si>
-  <si>
-    <t>A school with a single administrator.</t>
-  </si>
-  <si>
-    <t>The action is prevented - the control is unavailable, or it is blocked with a message explaining the school must retain at least one administrator - and the role is unchanged afterwards. [ASSUMED]</t>
-  </si>
-  <si>
-    <t>Added 2026-09-01 from the other team's TC_STF_011_N1. No counterpart existed anywhere in our register. Related but distinct from TST_STFP_TC_14, which checks an administrator can reach Remove admin rights on their own profile - this one checks what happens when doing so would leave the school with none.</t>
-  </si>
-  <si>
-    <t>Blocked at design time (skill rule 4): the precondition is a school with exactly one administrator. 3 July Test School 1 is shared and has several, and reducing it to one would break other suites. Unblock with a dedicated single-admin school.</t>
   </si>
 </sst>
 </file>
@@ -1655,7 +1319,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P58"/>
+  <dimension ref="A1:P41"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -1725,7 +1389,7 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>16</v>
@@ -1775,7 +1439,7 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>30</v>
@@ -1784,178 +1448,178 @@
         <v>31</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F3" s="3" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N3" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O3" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="P3" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="F4" s="3" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N4" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O4" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="P4" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="I5" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="L5" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N5" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O5" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="P5" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="K6" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="L6" s="3" t="s">
         <v>26</v>
@@ -1975,87 +1639,87 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="K7" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="I7" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="L7" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N7" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O7" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="P7" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="K8" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>26</v>
@@ -2075,137 +1739,137 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>21</v>
+        <v>74</v>
       </c>
       <c r="H9" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="K9" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O9" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="P9" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>21</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>81</v>
       </c>
       <c r="I10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J10" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="K10" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>84</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O10" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="P10" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>75</v>
-      </c>
       <c r="E11" s="3" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H11" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="K11" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="L11" s="3" t="s">
         <v>26</v>
@@ -2225,19 +1889,19 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>94</v>
+        <v>19</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>20</v>
@@ -2246,295 +1910,295 @@
         <v>21</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>98</v>
+        <v>57</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O12" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="P12" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="L13" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O13" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="P13" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O14" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="P14" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>114</v>
+        <v>86</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O15" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="P15" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>114</v>
+        <v>86</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="L16" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N16" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O16" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="P16" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>114</v>
+        <v>86</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="L17" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N17" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O17" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="P17" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>19</v>
@@ -2543,189 +2207,189 @@
         <v>20</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="L18" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O18" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="P18" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>134</v>
+        <v>21</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="L19" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N19" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O19" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="P19" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>23</v>
+        <v>134</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>23</v>
+        <v>109</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O20" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="P20" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
+        <v>26</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="G21" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="K21" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H21" s="3" t="s">
+      <c r="L21" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M21" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J21" s="3" t="s">
+      <c r="N21" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="O21" t="s">
         <v>145</v>
       </c>
-      <c r="K21" s="3" t="s">
+      <c r="P21" t="s">
         <v>146</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O21" t="s">
-        <v>38</v>
-      </c>
-      <c r="P21" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>147</v>
@@ -2734,28 +2398,28 @@
         <v>148</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>114</v>
+        <v>149</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>149</v>
+        <v>21</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>150</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>23</v>
+        <v>151</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>26</v>
@@ -2770,21 +2434,21 @@
         <v>28</v>
       </c>
       <c r="P22" t="s">
-        <v>29</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>19</v>
@@ -2793,39 +2457,39 @@
         <v>20</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>157</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>23</v>
+        <v>158</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>159</v>
+        <v>109</v>
       </c>
       <c r="L23" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N23" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O23" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="P23" t="s">
-        <v>39</v>
+        <v>154</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>160</v>
@@ -2834,157 +2498,157 @@
         <v>161</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>23</v>
+        <v>164</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O24" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="P24" t="s">
-        <v>39</v>
+        <v>154</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>21</v>
+        <v>170</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>57</v>
+        <v>172</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>137</v>
+        <v>174</v>
       </c>
       <c r="L25" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N25" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O25" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="P25" t="s">
-        <v>39</v>
+        <v>154</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>155</v>
-      </c>
       <c r="E26" s="3" t="s">
-        <v>94</v>
+        <v>19</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>21</v>
+        <v>177</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>23</v>
+        <v>179</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="L26" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>27</v>
+        <v>144</v>
       </c>
       <c r="N26" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O26" t="s">
-        <v>28</v>
+        <v>145</v>
       </c>
       <c r="P26" t="s">
-        <v>29</v>
+        <v>146</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>19</v>
@@ -2993,19 +2657,19 @@
         <v>20</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>181</v>
+        <v>109</v>
       </c>
       <c r="L27" s="3" t="s">
         <v>26</v>
@@ -3017,24 +2681,24 @@
         <v>26</v>
       </c>
       <c r="O27" t="s">
-        <v>182</v>
+        <v>28</v>
       </c>
       <c r="P27" t="s">
-        <v>183</v>
+        <v>154</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>184</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>186</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>19</v>
@@ -3043,48 +2707,48 @@
         <v>20</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>21</v>
+        <v>189</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>188</v>
+        <v>158</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L28" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N28" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O28" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="P28" t="s">
-        <v>191</v>
+        <v>154</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>19</v>
@@ -3093,48 +2757,48 @@
         <v>20</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>21</v>
+        <v>195</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>137</v>
+        <v>199</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>37</v>
+        <v>144</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O29" t="s">
-        <v>38</v>
+        <v>145</v>
       </c>
       <c r="P29" t="s">
-        <v>191</v>
+        <v>146</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>19</v>
@@ -3143,19 +2807,19 @@
         <v>20</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="L30" s="3" t="s">
         <v>26</v>
@@ -3170,42 +2834,42 @@
         <v>28</v>
       </c>
       <c r="P30" t="s">
-        <v>29</v>
+        <v>154</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>21</v>
+        <v>209</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>206</v>
+        <v>57</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="L31" s="3" t="s">
         <v>26</v>
@@ -3220,171 +2884,171 @@
         <v>28</v>
       </c>
       <c r="P31" t="s">
-        <v>29</v>
+        <v>154</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>94</v>
+        <v>19</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>21</v>
+        <v>215</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>27</v>
+        <v>144</v>
       </c>
       <c r="N32" s="3" t="s">
-        <v>215</v>
+        <v>26</v>
       </c>
       <c r="O32" t="s">
-        <v>28</v>
+        <v>145</v>
       </c>
       <c r="P32" t="s">
-        <v>29</v>
+        <v>146</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
+        <v>43</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E33" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>21</v>
+        <v>209</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>220</v>
+        <v>57</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L33" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="N33" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O33" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="P33" t="s">
-        <v>191</v>
+        <v>154</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>226</v>
+        <v>57</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L34" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>27</v>
+        <v>144</v>
       </c>
       <c r="N34" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O34" t="s">
-        <v>28</v>
+        <v>145</v>
       </c>
       <c r="P34" t="s">
-        <v>29</v>
+        <v>146</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>19</v>
@@ -3393,13 +3057,13 @@
         <v>20</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>234</v>
+        <v>57</v>
       </c>
       <c r="J35" s="3" t="s">
         <v>235</v>
@@ -3411,21 +3075,21 @@
         <v>26</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>37</v>
+        <v>144</v>
       </c>
       <c r="N35" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O35" t="s">
-        <v>38</v>
+        <v>145</v>
       </c>
       <c r="P35" t="s">
-        <v>191</v>
+        <v>146</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>237</v>
@@ -3434,13 +3098,13 @@
         <v>238</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>239</v>
@@ -3449,92 +3113,92 @@
         <v>240</v>
       </c>
       <c r="I36" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J36" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="J36" s="3" t="s">
+      <c r="K36" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="K36" s="3" t="s">
-        <v>243</v>
-      </c>
       <c r="L36" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>27</v>
+        <v>144</v>
       </c>
       <c r="N36" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O36" t="s">
-        <v>182</v>
+        <v>145</v>
       </c>
       <c r="P36" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="B37" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>245</v>
-      </c>
       <c r="D37" s="3" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="G37" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="K37" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="H37" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="K37" s="3" t="s">
-        <v>137</v>
-      </c>
       <c r="L37" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>37</v>
+        <v>144</v>
       </c>
       <c r="N37" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O37" t="s">
-        <v>38</v>
+        <v>145</v>
       </c>
       <c r="P37" t="s">
-        <v>191</v>
+        <v>146</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B38" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>250</v>
-      </c>
       <c r="D38" s="3" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>19</v>
@@ -3543,13 +3207,13 @@
         <v>20</v>
       </c>
       <c r="G38" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="H38" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="H38" s="3" t="s">
+      <c r="I38" s="3" t="s">
         <v>252</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>195</v>
       </c>
       <c r="J38" s="3" t="s">
         <v>253</v>
@@ -3561,21 +3225,21 @@
         <v>26</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>37</v>
+        <v>144</v>
       </c>
       <c r="N38" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O38" t="s">
-        <v>38</v>
+        <v>145</v>
       </c>
       <c r="P38" t="s">
-        <v>191</v>
+        <v>146</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>255</v>
@@ -3584,10 +3248,10 @@
         <v>256</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>20</v>
@@ -3611,21 +3275,21 @@
         <v>26</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>27</v>
+        <v>144</v>
       </c>
       <c r="N39" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O39" t="s">
-        <v>182</v>
+        <v>145</v>
       </c>
       <c r="P39" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>262</v>
@@ -3634,943 +3298,93 @@
         <v>263</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L40" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>27</v>
+        <v>144</v>
       </c>
       <c r="N40" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="O40" t="s">
-        <v>28</v>
-      </c>
-      <c r="P40" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O40" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="P40" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>199</v>
+        <v>273</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>23</v>
+        <v>275</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="L41" s="3" t="s">
         <v>26</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>37</v>
+        <v>278</v>
       </c>
       <c r="N41" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O41" t="s">
-        <v>38</v>
-      </c>
-      <c r="P41" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A42" s="3">
-        <v>41</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="H42" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="O41" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="K42" s="3" t="s">
+      <c r="P41" s="3" t="s">
         <v>280</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O42" t="s">
-        <v>38</v>
-      </c>
-      <c r="P42" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A43" s="3">
-        <v>42</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N43" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O43" t="s">
-        <v>182</v>
-      </c>
-      <c r="P43" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A44" s="3">
-        <v>43</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M44" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="N44" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O44" t="s">
-        <v>38</v>
-      </c>
-      <c r="P44" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A45" s="3">
-        <v>44</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O45" t="s">
-        <v>182</v>
-      </c>
-      <c r="P45" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A46" s="3">
-        <v>45</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M46" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N46" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O46" t="s">
-        <v>182</v>
-      </c>
-      <c r="P46" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A47" s="3">
-        <v>46</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O47" t="s">
-        <v>182</v>
-      </c>
-      <c r="P47" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A48" s="3">
-        <v>47</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M48" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N48" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O48" t="s">
-        <v>182</v>
-      </c>
-      <c r="P48" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A49" s="3">
-        <v>48</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M49" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N49" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O49" t="s">
-        <v>182</v>
-      </c>
-      <c r="P49" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A50" s="3">
-        <v>49</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J50" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="K50" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="L50" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M50" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N50" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O50" t="s">
-        <v>28</v>
-      </c>
-      <c r="P50" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A51" s="3">
-        <v>50</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J51" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="K51" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="L51" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M51" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N51" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O51" t="s">
-        <v>28</v>
-      </c>
-      <c r="P51" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A52" s="3">
-        <v>51</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N52" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O52" t="s">
-        <v>28</v>
-      </c>
-      <c r="P52" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A53" s="3">
-        <v>52</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="I53" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="J53" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="K53" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="L53" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M53" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N53" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O53" t="s">
-        <v>182</v>
-      </c>
-      <c r="P53" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A54" s="3">
-        <v>53</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="K54" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="L54" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M54" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N54" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O54" t="s">
-        <v>28</v>
-      </c>
-      <c r="P54" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A55" s="3">
-        <v>54</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="I55" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J55" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="K55" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="L55" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M55" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="N55" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="O55" t="s">
-        <v>359</v>
-      </c>
-      <c r="P55" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A56" s="3">
-        <v>55</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G56" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H56" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="I56" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J56" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="K56" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="L56" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M56" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N56" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O56" t="s">
-        <v>28</v>
-      </c>
-      <c r="P56" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="3">
-        <v>56</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N57" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="P57" s="3" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="3">
-        <v>57</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>361</v>
       </c>
     </row>
   </sheetData>

--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Staff/AdminApp_Staff_tab_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Staff/AdminApp_Staff_tab_test_cases.xlsx
@@ -102,7 +102,7 @@
     <t>Automated</t>
   </si>
   <si>
-    <t>Suite: adminStaffTab | 2026-09-16: Pass across 2 runs</t>
+    <t>Suite: adminStaffTab | Not executed in this audit - status carried over, treat as unverified</t>
   </si>
   <si>
     <t>TST_STFL_TC_3</t>
@@ -510,7 +510,7 @@
     <t>The row itself is the menu toggle — the whole row is a button with data-toggle="dropdown", and the menu holds exactly ONE item, View profile. There is no "Activate course materials" item as there is on the Students tab. teacher17aug2026@mailsac.com is the team-nominated teacher fixture for this school [confirmed with the team 2026-08-24].</t>
   </si>
   <si>
-    <t>Suite: adminStaffProfile | 2026-09-16: Pass across 2 runs</t>
+    <t>Suite: adminStaffProfile | Not executed in this audit - status carried over, treat as unverified</t>
   </si>
   <si>
     <t>TST_STFP_TC_2</t>
@@ -3325,16 +3325,16 @@
         <v>26</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>144</v>
+        <v>27</v>
       </c>
       <c r="N40" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O40" s="3" t="s">
-        <v>145</v>
+        <v>28</v>
       </c>
       <c r="P40" s="3" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
     </row>
     <row r="41" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
